--- a/BWI/bestwine_output/bestwine_Jordan.xlsx
+++ b/BWI/bestwine_output/bestwine_Jordan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AA29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3477,6 +3477,99 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Fyxx</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Fyxx</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>106667</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Amman Governorate</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>14 Al Mansourah</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11181</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://myfyxx.com</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>info@myfyxx.com</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fyxx/</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/myfyxx.jo</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/myfyxx</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>Hanna Nasser</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hanna-nasser-998835321</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
